--- a/Excel/SkillModelConfig.xlsx
+++ b/Excel/SkillModelConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>_ID</t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>彻地钉</t>
+  </si>
+  <si>
+    <t>剑二十三</t>
   </si>
   <si>
     <t>小火球</t>
@@ -355,12 +358,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1146,14 +1149,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <dimension ref="C3:F69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="3.5" style="2" customWidth="1"/>
+    <col min="1" max="1" width="5.6283185840708" style="2" customWidth="1"/>
+    <col min="2" max="2" width="3.50442477876106" style="2" customWidth="1"/>
     <col min="3" max="3" width="9" style="2"/>
-    <col min="4" max="4" width="16.25" style="2" customWidth="1"/>
-    <col min="5" max="6" width="14.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.2477876106195" style="2" customWidth="1"/>
+    <col min="5" max="6" width="14.2477876106195" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1339,32 +1342,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="4:4">
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="3:6">
-      <c r="C17" s="1">
-        <v>2001</v>
-      </c>
-      <c r="D17" s="1" t="s">
+    <row r="16" s="1" customFormat="1" spans="3:6">
+      <c r="C16" s="1">
+        <v>12</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
+      <c r="E16" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="4:4">
+      <c r="D17" s="2"/>
     </row>
     <row r="18" s="1" customFormat="1" spans="3:6">
       <c r="C18" s="1">
-        <v>2002</v>
-      </c>
-      <c r="D18" s="2" t="s">
+        <v>2001</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="1">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
@@ -1372,13 +1375,13 @@
     </row>
     <row r="19" s="1" customFormat="1" spans="3:6">
       <c r="C19" s="1">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E19" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F19" s="1">
         <v>1</v>
@@ -1386,7 +1389,7 @@
     </row>
     <row r="20" s="1" customFormat="1" spans="3:6">
       <c r="C20" s="1">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>23</v>
@@ -1400,13 +1403,13 @@
     </row>
     <row r="21" s="1" customFormat="1" spans="3:6">
       <c r="C21" s="1">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E21" s="1">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F21" s="1">
         <v>1</v>
@@ -1414,9 +1417,9 @@
     </row>
     <row r="22" s="1" customFormat="1" spans="3:6">
       <c r="C22" s="1">
-        <v>2006</v>
-      </c>
-      <c r="D22" s="1" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="1">
@@ -1428,27 +1431,27 @@
     </row>
     <row r="23" s="1" customFormat="1" spans="3:6">
       <c r="C23" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="12" customHeight="1" spans="3:6">
+      <c r="C24" s="1">
         <v>2007</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="3:6">
-      <c r="C24" s="1">
-        <v>2008</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E24" s="1">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F24" s="1">
         <v>1</v>
@@ -1456,44 +1459,44 @@
     </row>
     <row r="25" s="1" customFormat="1" spans="3:6">
       <c r="C25" s="1">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="3:6">
+      <c r="C26" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="1">
         <v>1.5</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F26" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="4:4">
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="3:6">
-      <c r="C27" s="1">
-        <v>3001</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1</v>
-      </c>
+    <row r="27" s="1" customFormat="1" spans="4:4">
+      <c r="D27" s="2"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="3:6">
       <c r="C28" s="1">
-        <v>3002</v>
-      </c>
-      <c r="D28" s="1" t="s">
+        <v>3001</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E28" s="1">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="F28" s="1">
         <v>1</v>
@@ -1501,13 +1504,13 @@
     </row>
     <row r="29" s="1" customFormat="1" spans="3:6">
       <c r="C29" s="1">
-        <v>3003</v>
-      </c>
-      <c r="D29" s="2" t="s">
+        <v>3002</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E29" s="1">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="F29" s="1">
         <v>1</v>
@@ -1515,7 +1518,7 @@
     </row>
     <row r="30" s="1" customFormat="1" spans="3:6">
       <c r="C30" s="1">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>32</v>
@@ -1529,7 +1532,7 @@
     </row>
     <row r="31" s="1" customFormat="1" spans="3:6">
       <c r="C31" s="1">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>33</v>
@@ -1543,9 +1546,9 @@
     </row>
     <row r="32" s="1" customFormat="1" spans="3:6">
       <c r="C32" s="1">
-        <v>3006</v>
-      </c>
-      <c r="D32" s="1" t="s">
+        <v>3005</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E32" s="1">
@@ -1557,9 +1560,9 @@
     </row>
     <row r="33" s="1" customFormat="1" spans="3:6">
       <c r="C33" s="1">
-        <v>3007</v>
-      </c>
-      <c r="D33" s="2" t="s">
+        <v>3006</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E33" s="1">
@@ -1571,7 +1574,7 @@
     </row>
     <row r="34" s="1" customFormat="1" spans="3:6">
       <c r="C34" s="1">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>36</v>
@@ -1585,7 +1588,7 @@
     </row>
     <row r="35" s="1" customFormat="1" spans="3:6">
       <c r="C35" s="1">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>37</v>
@@ -1597,52 +1600,63 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" spans="4:4">
-      <c r="D36" s="2"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="3:6">
-      <c r="C37" s="1">
+    <row r="36" s="1" customFormat="1" spans="3:6">
+      <c r="C36" s="1">
+        <v>3009</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="F36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="4:4">
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="3:6">
+      <c r="C38" s="1">
         <v>9001</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="D38" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="1">
         <v>0.2</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F38" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1"/>
     <row r="39" s="1" customFormat="1"/>
-    <row r="40" s="1" customFormat="1" spans="4:4">
-      <c r="D40" s="2"/>
-    </row>
-    <row r="44" s="1" customFormat="1" spans="4:4">
-      <c r="D44" s="2"/>
-    </row>
-    <row r="46" s="1" customFormat="1"/>
-    <row r="47" s="1" customFormat="1" spans="4:4">
-      <c r="D47" s="2"/>
-    </row>
+    <row r="40" s="1" customFormat="1"/>
+    <row r="41" s="1" customFormat="1" spans="4:4">
+      <c r="D41" s="2"/>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="4:4">
+      <c r="D45" s="2"/>
+    </row>
+    <row r="47" s="1" customFormat="1"/>
     <row r="48" s="1" customFormat="1" spans="4:4">
       <c r="D48" s="2"/>
     </row>
-    <row r="49" s="1" customFormat="1"/>
-    <row r="50" s="1" customFormat="1" spans="4:4">
-      <c r="D50" s="2"/>
-    </row>
+    <row r="49" s="1" customFormat="1" spans="4:4">
+      <c r="D49" s="2"/>
+    </row>
+    <row r="50" s="1" customFormat="1"/>
     <row r="51" s="1" customFormat="1" spans="4:4">
       <c r="D51" s="2"/>
     </row>
     <row r="52" s="1" customFormat="1" spans="4:4">
       <c r="D52" s="2"/>
     </row>
-    <row r="53" s="1" customFormat="1"/>
-    <row r="54" s="1" customFormat="1" spans="4:4">
-      <c r="D54" s="2"/>
-    </row>
+    <row r="53" s="1" customFormat="1" spans="4:4">
+      <c r="D53" s="2"/>
+    </row>
+    <row r="54" s="1" customFormat="1"/>
     <row r="55" s="1" customFormat="1" spans="4:4">
       <c r="D55" s="2"/>
     </row>
@@ -1652,36 +1666,39 @@
     <row r="57" s="1" customFormat="1" spans="4:4">
       <c r="D57" s="2"/>
     </row>
-    <row r="58" s="1" customFormat="1"/>
-    <row r="59" s="1" customFormat="1" spans="4:4">
-      <c r="D59" s="2"/>
-    </row>
+    <row r="58" s="1" customFormat="1" spans="4:4">
+      <c r="D58" s="2"/>
+    </row>
+    <row r="59" s="1" customFormat="1"/>
     <row r="60" s="1" customFormat="1" spans="4:4">
       <c r="D60" s="2"/>
     </row>
-    <row r="61" s="1" customFormat="1"/>
-    <row r="62" s="1" customFormat="1" spans="4:4">
-      <c r="D62" s="2"/>
-    </row>
+    <row r="61" s="1" customFormat="1" spans="4:4">
+      <c r="D61" s="2"/>
+    </row>
+    <row r="62" s="1" customFormat="1"/>
     <row r="63" s="1" customFormat="1" spans="4:4">
       <c r="D63" s="2"/>
     </row>
     <row r="64" s="1" customFormat="1" spans="4:4">
       <c r="D64" s="2"/>
     </row>
-    <row r="65" s="1" customFormat="1"/>
-    <row r="66" s="1" customFormat="1" spans="4:4">
-      <c r="D66" s="2"/>
-    </row>
+    <row r="65" s="1" customFormat="1" spans="4:4">
+      <c r="D65" s="2"/>
+    </row>
+    <row r="66" s="1" customFormat="1"/>
     <row r="67" s="1" customFormat="1" spans="4:4">
       <c r="D67" s="2"/>
     </row>
     <row r="68" s="1" customFormat="1" spans="4:4">
       <c r="D68" s="2"/>
     </row>
+    <row r="69" s="1" customFormat="1" spans="4:4">
+      <c r="D69" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 D3:D5 E3:E5 F3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillModelConfig.xlsx
+++ b/Excel/SkillModelConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
   <si>
     <t>_ID</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>召唤月灵</t>
+  </si>
+  <si>
+    <t>飓风破</t>
   </si>
   <si>
     <t>普攻</t>
@@ -358,12 +361,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1149,7 +1152,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F69"/>
+  <dimension ref="C3:F71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="5.6283185840708" style="2" customWidth="1"/>
@@ -1617,84 +1620,101 @@
     <row r="37" s="1" customFormat="1" spans="4:4">
       <c r="D37" s="2"/>
     </row>
-    <row r="38" s="1" customFormat="1" spans="3:6">
+    <row r="38" s="1" customFormat="1" ht="12" customHeight="1" spans="3:6">
       <c r="C38" s="1">
+        <v>4004</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="4:4">
+      <c r="D39" s="2"/>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="3:6">
+      <c r="C40" s="1">
         <v>9001</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E38" s="1">
+      <c r="D40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" s="1">
         <v>0.2</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F40" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1"/>
-    <row r="40" s="1" customFormat="1"/>
-    <row r="41" s="1" customFormat="1" spans="4:4">
-      <c r="D41" s="2"/>
-    </row>
-    <row r="45" s="1" customFormat="1" spans="4:4">
-      <c r="D45" s="2"/>
-    </row>
-    <row r="47" s="1" customFormat="1"/>
-    <row r="48" s="1" customFormat="1" spans="4:4">
-      <c r="D48" s="2"/>
-    </row>
-    <row r="49" s="1" customFormat="1" spans="4:4">
-      <c r="D49" s="2"/>
-    </row>
-    <row r="50" s="1" customFormat="1"/>
+    <row r="41" s="1" customFormat="1"/>
+    <row r="42" s="1" customFormat="1"/>
+    <row r="43" s="1" customFormat="1" spans="4:4">
+      <c r="D43" s="2"/>
+    </row>
+    <row r="47" s="1" customFormat="1" spans="4:4">
+      <c r="D47" s="2"/>
+    </row>
+    <row r="49" s="1" customFormat="1"/>
+    <row r="50" s="1" customFormat="1" spans="4:4">
+      <c r="D50" s="2"/>
+    </row>
     <row r="51" s="1" customFormat="1" spans="4:4">
       <c r="D51" s="2"/>
     </row>
-    <row r="52" s="1" customFormat="1" spans="4:4">
-      <c r="D52" s="2"/>
-    </row>
+    <row r="52" s="1" customFormat="1"/>
     <row r="53" s="1" customFormat="1" spans="4:4">
       <c r="D53" s="2"/>
     </row>
-    <row r="54" s="1" customFormat="1"/>
+    <row r="54" s="1" customFormat="1" spans="4:4">
+      <c r="D54" s="2"/>
+    </row>
     <row r="55" s="1" customFormat="1" spans="4:4">
       <c r="D55" s="2"/>
     </row>
-    <row r="56" s="1" customFormat="1" spans="4:4">
-      <c r="D56" s="2"/>
-    </row>
+    <row r="56" s="1" customFormat="1"/>
     <row r="57" s="1" customFormat="1" spans="4:4">
       <c r="D57" s="2"/>
     </row>
     <row r="58" s="1" customFormat="1" spans="4:4">
       <c r="D58" s="2"/>
     </row>
-    <row r="59" s="1" customFormat="1"/>
+    <row r="59" s="1" customFormat="1" spans="4:4">
+      <c r="D59" s="2"/>
+    </row>
     <row r="60" s="1" customFormat="1" spans="4:4">
       <c r="D60" s="2"/>
     </row>
-    <row r="61" s="1" customFormat="1" spans="4:4">
-      <c r="D61" s="2"/>
-    </row>
-    <row r="62" s="1" customFormat="1"/>
+    <row r="61" s="1" customFormat="1"/>
+    <row r="62" s="1" customFormat="1" spans="4:4">
+      <c r="D62" s="2"/>
+    </row>
     <row r="63" s="1" customFormat="1" spans="4:4">
       <c r="D63" s="2"/>
     </row>
-    <row r="64" s="1" customFormat="1" spans="4:4">
-      <c r="D64" s="2"/>
-    </row>
+    <row r="64" s="1" customFormat="1"/>
     <row r="65" s="1" customFormat="1" spans="4:4">
       <c r="D65" s="2"/>
     </row>
-    <row r="66" s="1" customFormat="1"/>
+    <row r="66" s="1" customFormat="1" spans="4:4">
+      <c r="D66" s="2"/>
+    </row>
     <row r="67" s="1" customFormat="1" spans="4:4">
       <c r="D67" s="2"/>
     </row>
-    <row r="68" s="1" customFormat="1" spans="4:4">
-      <c r="D68" s="2"/>
-    </row>
+    <row r="68" s="1" customFormat="1"/>
     <row r="69" s="1" customFormat="1" spans="4:4">
       <c r="D69" s="2"/>
+    </row>
+    <row r="70" s="1" customFormat="1" spans="4:4">
+      <c r="D70" s="2"/>
+    </row>
+    <row r="71" s="1" customFormat="1" spans="4:4">
+      <c r="D71" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/SkillModelConfig.xlsx
+++ b/Excel/SkillModelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1153,17 +1153,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:F71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="5.6283185840708" style="2" customWidth="1"/>
-    <col min="2" max="2" width="3.50442477876106" style="2" customWidth="1"/>
+    <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="3.50833333333333" style="2" customWidth="1"/>
     <col min="3" max="3" width="9" style="2"/>
-    <col min="4" max="4" width="16.2477876106195" style="2" customWidth="1"/>
-    <col min="5" max="6" width="14.2477876106195" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.25" style="2" customWidth="1"/>
+    <col min="5" max="6" width="14.25" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6">
+    <row r="3" ht="13.5" spans="3:6">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="3:6">
+    <row r="4" ht="13.5" spans="3:6">
       <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="3:6">
+    <row r="5" ht="13.5" spans="3:6">
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>39</v>
       </c>
       <c r="E38" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F38" s="1">
         <v>1</v>

--- a/Excel/SkillModelConfig.xlsx
+++ b/Excel/SkillModelConfig.xlsx
@@ -361,12 +361,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1624,11 +1624,11 @@
       <c r="C38" s="1">
         <v>4004</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E38" s="1">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F38" s="1">
         <v>1</v>
